--- a/Revision/01_需蔡老師補做資料表/table3_internal_cv_performance_with_ci.xlsx
+++ b/Revision/01_需蔡老師補做資料表/table3_internal_cv_performance_with_ci.xlsx
@@ -562,92 +562,92 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.875116202600234</v>
+        <v>0.8878214970849616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.875 (0.870-0.880)</t>
+          <t>0.888 (0.883-0.893)</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.002741446639131183</v>
+        <v>0.002658209121474978</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8499225973808627</v>
+        <v>0.8657378352370194</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.850 (0.846-0.853)</t>
+          <t>0.866 (0.862-0.869)</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.001850421232283956</v>
+        <v>0.001902548059977659</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7739837398373983</v>
+        <v>0.7877266387726639</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.774 (0.760-0.787)</t>
+          <t>0.788 (0.775-0.799)</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.006839274842900723</v>
+        <v>0.006305221960701594</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4514415781487102</v>
+        <v>0.5356600910470409</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.451 (0.438-0.464)</t>
+          <t>0.536 (0.523-0.549)</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.006963084998175547</v>
+        <v>0.006966224317926071</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4514415781487102</v>
+        <v>0.5356600910470409</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.451 (0.438-0.464)</t>
+          <t>0.536 (0.523-0.549)</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.006963084998175547</v>
+        <v>0.006966224317926071</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9626925760910409</v>
+        <v>0.9591497128133555</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.963 (0.960-0.965)</t>
+          <t>0.959 (0.956-0.962)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>0.001350001721432022</v>
+        <v>0.0014490678230926</v>
       </c>
       <c r="T2" t="n">
-        <v>0.570264765784114</v>
+        <v>0.6376877046403975</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.570 (0.557-0.582)</t>
+          <t>0.638 (0.626-0.649)</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>0.006501399451872501</v>
+        <v>0.005966366215237637</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1085531093483734</v>
+        <v>0.100535925970357</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.109 (0.107-0.110)</t>
+          <t>0.101 (0.099-0.103)</t>
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>0.0009906047096349109</v>
+        <v>0.001053244055373949</v>
       </c>
     </row>
     <row r="3">
@@ -657,92 +657,92 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.794940837628867</v>
+        <v>0.8570589243556253</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.795 (0.788-0.802)</t>
+          <t>0.857 (0.851-0.863)</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.003512313894596773</v>
+        <v>0.00313596396568984</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7920589096690515</v>
+        <v>0.8408853186059161</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.792 (0.789-0.796)</t>
+          <t>0.841 (0.837-0.844)</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.001710190262805738</v>
+        <v>0.002078360419609667</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5818872017353579</v>
+        <v>0.6985671803190051</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.582 (0.561-0.604)</t>
+          <t>0.699 (0.685-0.710)</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.01088636838694605</v>
+        <v>0.006662533462983841</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2035280728376328</v>
+        <v>0.4901365705614568</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.204 (0.192-0.215)</t>
+          <t>0.490 (0.476-0.505)</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.006014730855570934</v>
+        <v>0.007362615558429206</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2035280728376328</v>
+        <v>0.4901365705614568</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.204 (0.192-0.215)</t>
+          <t>0.490 (0.476-0.505)</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.006014730855570934</v>
+        <v>0.007362615558429206</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9586129153470395</v>
+        <v>0.9401470825057706</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.959 (0.956-0.961)</t>
+          <t>0.940 (0.936-0.943)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0.001401284459961117</v>
+        <v>0.001672227414890983</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3015739179314221</v>
+        <v>0.5760784750863894</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.302 (0.286-0.316)</t>
+          <t>0.576 (0.563-0.588)</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.007638059676933001</v>
+        <v>0.006468217008686509</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1406598136113784</v>
+        <v>0.1155339721623951</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.141 (0.139-0.142)</t>
+          <t>0.116 (0.114-0.118)</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>0.0008708669629296099</v>
+        <v>0.001131021898027362</v>
       </c>
     </row>
     <row r="4">
@@ -752,92 +752,92 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.874027853882915</v>
+        <v>0.884619635619599</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.874 (0.869-0.879)</t>
+          <t>0.885 (0.879-0.890)</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.002774924652665959</v>
+        <v>0.002763033449737988</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8534370946822308</v>
+        <v>0.8620559809213003</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.853 (0.850-0.857)</t>
+          <t>0.862 (0.858-0.866)</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.001815632826261324</v>
+        <v>0.001858582769917357</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7893359502780504</v>
+        <v>0.7908689248895434</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.789 (0.775-0.801)</t>
+          <t>0.791 (0.778-0.803)</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.006874193104678269</v>
+        <v>0.006392088771379686</v>
       </c>
       <c r="K4" t="n">
-        <v>0.457701062215478</v>
+        <v>0.5092943854324734</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.458 (0.444-0.471)</t>
+          <t>0.509 (0.496-0.524)</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.006767546728699452</v>
+        <v>0.006871737318779085</v>
       </c>
       <c r="N4" t="n">
-        <v>0.457701062215478</v>
+        <v>0.5092943854324734</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.458 (0.444-0.471)</t>
+          <t>0.509 (0.496-0.524)</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.006767546728699452</v>
+        <v>0.006871737318779085</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9654302431692522</v>
+        <v>0.9618873798915669</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.965 (0.963-0.968)</t>
+          <t>0.962 (0.959-0.964)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.001340909869745076</v>
+        <v>0.001381055248541993</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5794212990755193</v>
+        <v>0.6195915541709934</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.579 (0.567-0.591)</t>
+          <t>0.620 (0.608-0.632)</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.006318164337424361</v>
+        <v>0.006056041789931202</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1099480207271066</v>
+        <v>0.1034446767029077</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.110 (0.108-0.112)</t>
+          <t>0.103 (0.102-0.105)</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>0.0009354150230713658</v>
+        <v>0.0009781724466425103</v>
       </c>
     </row>
     <row r="5">
@@ -847,92 +847,92 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8567555502943791</v>
+        <v>0.87062913273975</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.857 (0.851-0.863)</t>
+          <t>0.871 (0.865-0.877)</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.003149483091092884</v>
+        <v>0.003055082183874394</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8456549935149157</v>
+        <v>0.857997573323292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.846 (0.842-0.850)</t>
+          <t>0.858 (0.854-0.861)</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.002095859615204326</v>
+        <v>0.001906329769395807</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7156088259329882</v>
+        <v>0.7488076311605724</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.716 (0.702-0.728)</t>
+          <t>0.749 (0.736-0.759)</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.006784088060705915</v>
+        <v>0.006101488258564672</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4982928679817906</v>
+        <v>0.5360394537177542</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.498 (0.485-0.512)</t>
+          <t>0.536 (0.523-0.550)</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.007218597895775697</v>
+        <v>0.006946812313556371</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4982928679817906</v>
+        <v>0.5360394537177542</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.498 (0.485-0.512)</t>
+          <t>0.536 (0.523-0.550)</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.007218597895775697</v>
+        <v>0.006946812313556371</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9439583445166139</v>
+        <v>0.9491116001932471</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.944 (0.941-0.947)</t>
+          <t>0.949 (0.946-0.952)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0.001644393163484858</v>
+        <v>0.001545557867135592</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5874986022587498</v>
+        <v>0.6248065443289852</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.587 (0.576-0.600)</t>
+          <t>0.625 (0.614-0.636)</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.006436284033129231</v>
+        <v>0.005826934104863538</v>
       </c>
       <c r="W5" t="n">
-        <v>0.113628580940174</v>
+        <v>0.1059438193770698</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.114 (0.111-0.116)</t>
+          <t>0.106 (0.104-0.108)</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>0.001195690450049115</v>
+        <v>0.001197239767271253</v>
       </c>
     </row>
     <row r="6">
@@ -942,92 +942,92 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.796773412454076</v>
+        <v>0.8570589243556253</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.797 (0.790-0.804)</t>
+          <t>0.857 (0.851-0.863)</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.003512032661599331</v>
+        <v>0.00313596396568984</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7919752311618761</v>
+        <v>0.8408853186059161</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.792 (0.789-0.795)</t>
+          <t>0.841 (0.837-0.844)</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.001678022480691072</v>
+        <v>0.002078360419609667</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5806451612903226</v>
+        <v>0.6985671803190051</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.581 (0.561-0.601)</t>
+          <t>0.699 (0.685-0.710)</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.0106605244603139</v>
+        <v>0.006662533462983841</v>
       </c>
       <c r="K6" t="n">
-        <v>0.204855842185129</v>
+        <v>0.4901365705614568</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.205 (0.193-0.216)</t>
+          <t>0.490 (0.476-0.505)</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.005868991605459884</v>
+        <v>0.007362615558429206</v>
       </c>
       <c r="N6" t="n">
-        <v>0.204855842185129</v>
+        <v>0.4901365705614568</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.205 (0.193-0.216)</t>
+          <t>0.490 (0.476-0.505)</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.005868991605459884</v>
+        <v>0.007362615558429206</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9581297976273552</v>
+        <v>0.9401470825057706</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0.958 (0.955-0.961)</t>
+          <t>0.940 (0.936-0.943)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>0.001430715631398122</v>
+        <v>0.001672227414890983</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3028603477285474</v>
+        <v>0.5760784750863894</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.303 (0.289-0.317)</t>
+          <t>0.576 (0.563-0.588)</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>0.007412234867623444</v>
+        <v>0.006468217008686509</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1401536822026062</v>
+        <v>0.1155339721623951</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.140 (0.138-0.142)</t>
+          <t>0.116 (0.114-0.118)</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>0.0008821238461818834</v>
+        <v>0.001131021898027362</v>
       </c>
     </row>
     <row r="7">
@@ -1037,92 +1037,92 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7956643330910549</v>
+        <v>0.8551964957714778</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.796 (0.789-0.803)</t>
+          <t>0.855 (0.849-0.862)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.003497789787918302</v>
+        <v>0.003159190525611514</v>
       </c>
       <c r="E7" t="n">
-        <v>0.792142588176227</v>
+        <v>0.8411363541274424</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.792 (0.789-0.795)</t>
+          <t>0.841 (0.837-0.845)</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.001681962263562982</v>
+        <v>0.002057998356927058</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5829694323144105</v>
+        <v>0.7038982582250484</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.583 (0.562-0.602)</t>
+          <t>0.704 (0.690-0.716)</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.01084434234177484</v>
+        <v>0.006678779871511963</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2025796661608498</v>
+        <v>0.4829286798179059</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.203 (0.191-0.215)</t>
+          <t>0.483 (0.468-0.497)</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.005867380083358268</v>
+        <v>0.007326875304625805</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2025796661608498</v>
+        <v>0.4829286798179059</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.203 (0.191-0.215)</t>
+          <t>0.483 (0.468-0.497)</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.005867380083358268</v>
+        <v>0.007326875304625805</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9589886735734607</v>
+        <v>0.9425089913575608</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.959 (0.956-0.962)</t>
+          <t>0.943 (0.939-0.945)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>0.001425573703204235</v>
+        <v>0.00161686191985145</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3006756756756757</v>
+        <v>0.5728428394645066</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.301 (0.287-0.316)</t>
+          <t>0.573 (0.560-0.585)</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.007455994078140434</v>
+        <v>0.006513738292120521</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1404595177574103</v>
+        <v>0.1162297755497152</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.140 (0.139-0.142)</t>
+          <t>0.116 (0.114-0.118)</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>0.0008705350884822573</v>
+        <v>0.00111223510219239</v>
       </c>
     </row>
     <row r="8">
@@ -1132,92 +1132,92 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7956507298775686</v>
+        <v>0.8558243818215125</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.796 (0.789-0.803)</t>
+          <t>0.856 (0.850-0.862)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.003496574009899791</v>
+        <v>0.003156027153565154</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7921007489226393</v>
+        <v>0.8409689971130915</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.792 (0.789-0.795)</t>
+          <t>0.841 (0.837-0.845)</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.001679530586204995</v>
+        <v>0.002044715006930562</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5829228243021346</v>
+        <v>0.7004633415099483</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.583 (0.562-0.602)</t>
+          <t>0.700 (0.687-0.713)</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.01084936691749164</v>
+        <v>0.006607511754967338</v>
       </c>
       <c r="K8" t="n">
-        <v>0.20201062215478</v>
+        <v>0.4874810318664644</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.202 (0.191-0.214)</t>
+          <t>0.487 (0.473-0.502)</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.00587942124153032</v>
+        <v>0.007230888493252334</v>
       </c>
       <c r="N8" t="n">
-        <v>0.20201062215478</v>
+        <v>0.4874810318664644</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.202 (0.191-0.214)</t>
+          <t>0.487 (0.473-0.502)</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.00587942124153032</v>
+        <v>0.007230888493252334</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.959096033066724</v>
+        <v>0.9410059584518761</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.959 (0.956-0.962)</t>
+          <t>0.941 (0.937-0.944)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>0.00142391107340393</v>
+        <v>0.001640147767301408</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3000422594731652</v>
+        <v>0.5748797673638295</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.300 (0.286-0.315)</t>
+          <t>0.575 (0.562-0.586)</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>0.007473359997474375</v>
+        <v>0.006385744268303126</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1404655665455319</v>
+        <v>0.1159069143252541</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.140 (0.139-0.142)</t>
+          <t>0.116 (0.114-0.118)</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>0.0008696571161069652</v>
+        <v>0.001121045380785139</v>
       </c>
     </row>
     <row r="9">
@@ -1227,92 +1227,92 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7956594304358952</v>
+        <v>0.8555251823991361</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.796 (0.789-0.803)</t>
+          <t>0.856 (0.850-0.862)</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.003497318407858139</v>
+        <v>0.003157444536591365</v>
       </c>
       <c r="E9" t="n">
-        <v>0.792142588176227</v>
+        <v>0.841052675620267</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.792 (0.789-0.795)</t>
+          <t>0.841 (0.837-0.845)</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.001687099588670582</v>
+        <v>0.002046402932254512</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5829694323144105</v>
+        <v>0.7025020621391257</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.583 (0.562-0.602)</t>
+          <t>0.703 (0.689-0.714)</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.0108695012774475</v>
+        <v>0.006644272532736765</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2025796661608498</v>
+        <v>0.4846358118361153</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.203 (0.191-0.215)</t>
+          <t>0.485 (0.470-0.499)</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.005891002352943747</v>
+        <v>0.007257142454861689</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2025796661608498</v>
+        <v>0.4846358118361153</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.203 (0.191-0.215)</t>
+          <t>0.485 (0.470-0.499)</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.005891002352943747</v>
+        <v>0.007257142454861689</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9589886735734607</v>
+        <v>0.9419185141446133</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.959 (0.956-0.962)</t>
+          <t>0.942 (0.938-0.945)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>0.001425573703204235</v>
+        <v>0.001626241493084626</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3006756756756757</v>
+        <v>0.5735772814008306</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.301 (0.286-0.316)</t>
+          <t>0.574 (0.561-0.585)</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>0.007486806258920207</v>
+        <v>0.006437054841160304</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1404622262209613</v>
+        <v>0.116068282947681</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.140 (0.139-0.142)</t>
+          <t>0.116 (0.114-0.118)</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>0.0008701086428143687</v>
+        <v>0.001116392432279363</v>
       </c>
     </row>
   </sheetData>
